--- a/Railway_Stations_in_Mumbai.xlsx
+++ b/Railway_Stations_in_Mumbai.xlsx
@@ -14157,55 +14157,23 @@
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Chembur</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>चेम्बुर</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>चेंबूर</t>
-        </is>
-      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>Q17050476</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>en:Chembur monorail station</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
+      <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr"/>
@@ -14213,21 +14181,9 @@
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
@@ -14280,7 +14236,7 @@
       <c r="CA94" t="inlineStr"/>
       <c r="CB94" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Suburban/Local Rail</t>
         </is>
       </c>
     </row>
@@ -14291,42 +14247,18 @@
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Bhakti Park</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>भक्ती पार्क</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>Q17065178</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>en:Bhakti Park monorail station</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
@@ -14339,16 +14271,8 @@
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr"/>
       <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="inlineStr"/>
@@ -14402,7 +14326,7 @@
       <c r="CA95" t="inlineStr"/>
       <c r="CB95" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -14413,42 +14337,18 @@
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Wadala Depot</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>वडाळा डेपो</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>Q17100205</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>en:Wadala Depot monorail station</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
@@ -14462,11 +14362,7 @@
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="inlineStr"/>
@@ -14520,7 +14416,7 @@
       <c r="CA96" t="inlineStr"/>
       <c r="CB96" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -14531,42 +14427,18 @@
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Mysore Colony</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>मैसुर कॉलनी</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Q17076201</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>en:Mysore Colony monorail station</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
@@ -14579,16 +14451,8 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr"/>
@@ -14642,7 +14506,7 @@
       <c r="CA97" t="inlineStr"/>
       <c r="CB97" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -14653,42 +14517,18 @@
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Bharat Petroleum</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>भारत पेट्रोलियम</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>Q15733864</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>en:Bharat Petroleum monorail station</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
@@ -14701,16 +14541,8 @@
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr"/>
       <c r="AE98" t="inlineStr"/>
@@ -14764,7 +14596,7 @@
       <c r="CA98" t="inlineStr"/>
       <c r="CB98" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -14775,42 +14607,18 @@
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>VNP &amp; RC Marg Junction</t>
-        </is>
-      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>व्हि एन पी आणि आर सी मार्ग जंक्शन</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Q18357722</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>en:VNP and RC Marg Junction monorail station</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
@@ -14823,16 +14631,8 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr"/>
       <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="inlineStr"/>
@@ -14886,7 +14686,7 @@
       <c r="CA99" t="inlineStr"/>
       <c r="CB99" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -14897,37 +14697,17 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Fertilizer Township</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>फर्टीलाईझर टाऊनशिप</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>Q15733865</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
@@ -14941,16 +14721,8 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
@@ -15004,7 +14776,7 @@
       <c r="CA100" t="inlineStr"/>
       <c r="CB100" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15015,39 +14787,19 @@
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Wadala Bridge</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>वडाला ब्रिज</t>
-        </is>
-      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Wadala Bridge</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -15055,28 +14807,12 @@
       <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr"/>
       <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr">
-        <is>
-          <t>Vadala Bridge</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Vadala Bridge</t>
-        </is>
-      </c>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="inlineStr"/>
@@ -15130,7 +14866,7 @@
       <c r="CA101" t="inlineStr"/>
       <c r="CB101" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15141,33 +14877,17 @@
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Acharya Atre Nagar</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Q63346707</t>
-        </is>
-      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
@@ -15181,16 +14901,8 @@
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr"/>
       <c r="AE102" t="inlineStr"/>
@@ -15244,7 +14956,7 @@
       <c r="CA102" t="inlineStr"/>
       <c r="CB102" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15255,37 +14967,17 @@
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Ambedkar Nagar</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>अम्बेडकर नगर</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>Q23926706</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
@@ -15299,16 +14991,8 @@
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr"/>
       <c r="AE103" t="inlineStr"/>
@@ -15362,7 +15046,7 @@
       <c r="CA103" t="inlineStr"/>
       <c r="CB103" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15373,37 +15057,17 @@
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Dadar East</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>दादर पूर्व</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>Q63346705</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
@@ -15417,16 +15081,8 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="inlineStr"/>
@@ -15480,7 +15136,7 @@
       <c r="CA104" t="inlineStr"/>
       <c r="CB104" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15491,37 +15147,17 @@
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Guru Tegh Bahadur Nagar</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>गुरु तेग़ बहादुर नगर</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>Q63346710</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
@@ -15535,16 +15171,8 @@
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr"/>
       <c r="AD105" t="inlineStr"/>
       <c r="AE105" t="inlineStr"/>
@@ -15559,11 +15187,7 @@
       <c r="AN105" t="inlineStr"/>
       <c r="AO105" t="inlineStr"/>
       <c r="AP105" t="inlineStr"/>
-      <c r="AQ105" t="inlineStr">
-        <is>
-          <t>GTB Nagar</t>
-        </is>
-      </c>
+      <c r="AQ105" t="inlineStr"/>
       <c r="AR105" t="inlineStr"/>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="inlineStr"/>
@@ -15602,7 +15226,7 @@
       <c r="CA105" t="inlineStr"/>
       <c r="CB105" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Suburban/Local Rail</t>
         </is>
       </c>
     </row>
@@ -15613,35 +15237,19 @@
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Sant Gadge Maharaj Chowk</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>Sant Gadge Maharaj Chowk</t>
-        </is>
-      </c>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr"/>
@@ -15649,28 +15257,12 @@
       <c r="T106" t="inlineStr"/>
       <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr">
-        <is>
-          <t>Jacob Circle</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Jacob Circle</t>
-        </is>
-      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr"/>
       <c r="AE106" t="inlineStr"/>
@@ -15724,7 +15316,7 @@
       <c r="CA106" t="inlineStr"/>
       <c r="CB106" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15735,33 +15327,17 @@
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Mint Colony</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>Q63592634</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
@@ -15775,16 +15351,8 @@
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr"/>
@@ -15838,7 +15406,7 @@
       <c r="CA107" t="inlineStr"/>
       <c r="CB107" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15849,33 +15417,17 @@
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Naigaon</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>Q63346704</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
@@ -15889,16 +15441,8 @@
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr"/>
       <c r="AE108" t="inlineStr"/>
@@ -15952,7 +15496,7 @@
       <c r="CA108" t="inlineStr"/>
       <c r="CB108" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -15963,52 +15507,20 @@
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Chembur</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>चेंबूर</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>चेंबूर</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Mumbai Metro Line 2</t>
-        </is>
-      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>Chembur</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
@@ -16020,11 +15532,7 @@
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
       <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr"/>
       <c r="AE109" t="inlineStr"/>
@@ -16041,11 +15549,7 @@
       <c r="AP109" t="inlineStr"/>
       <c r="AQ109" t="inlineStr"/>
       <c r="AR109" t="inlineStr"/>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="inlineStr"/>
       <c r="AU109" t="inlineStr"/>
       <c r="AV109" t="inlineStr"/>
@@ -16082,7 +15586,7 @@
       <c r="CA109" t="inlineStr"/>
       <c r="CB109" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16093,47 +15597,23 @@
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Dahanukarwadi</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>डहाणूकरवाडी</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>Q116266997</t>
-        </is>
-      </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
@@ -16142,11 +15622,7 @@
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
       <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr"/>
       <c r="AE110" t="inlineStr"/>
@@ -16163,11 +15639,7 @@
       <c r="AP110" t="inlineStr"/>
       <c r="AQ110" t="inlineStr"/>
       <c r="AR110" t="inlineStr"/>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="inlineStr"/>
       <c r="AU110" t="inlineStr"/>
       <c r="AV110" t="inlineStr"/>
@@ -16204,7 +15676,7 @@
       <c r="CA110" t="inlineStr"/>
       <c r="CB110" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16215,30 +15687,14 @@
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Kandivali (West)</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>कांदिवली (पश्चिम)</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
@@ -16247,11 +15703,7 @@
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr"/>
@@ -16260,11 +15712,7 @@
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
       <c r="AA111" t="inlineStr"/>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr"/>
@@ -16281,11 +15729,7 @@
       <c r="AP111" t="inlineStr"/>
       <c r="AQ111" t="inlineStr"/>
       <c r="AR111" t="inlineStr"/>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="inlineStr"/>
       <c r="AU111" t="inlineStr"/>
       <c r="AV111" t="inlineStr"/>
@@ -16322,7 +15766,7 @@
       <c r="CA111" t="inlineStr"/>
       <c r="CB111" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16333,37 +15777,17 @@
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Borivali (West)</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>बोरिवली (पश्चिम)</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>Q116266994</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
@@ -16378,11 +15802,7 @@
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
       <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr"/>
@@ -16399,11 +15819,7 @@
       <c r="AP112" t="inlineStr"/>
       <c r="AQ112" t="inlineStr"/>
       <c r="AR112" t="inlineStr"/>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="inlineStr"/>
       <c r="AU112" t="inlineStr"/>
       <c r="AV112" t="inlineStr"/>
@@ -16440,7 +15856,7 @@
       <c r="CA112" t="inlineStr"/>
       <c r="CB112" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16451,30 +15867,14 @@
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Mandapeshwar - I.C. Colony</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>मंडपेश्वर - आय.सी. कॉलनी</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
@@ -16487,20 +15887,12 @@
       <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Mandapeshwar</t>
-        </is>
-      </c>
+      <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
       <c r="AA113" t="inlineStr"/>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr"/>
       <c r="AD113" t="inlineStr"/>
       <c r="AE113" t="inlineStr"/>
@@ -16517,11 +15909,7 @@
       <c r="AP113" t="inlineStr"/>
       <c r="AQ113" t="inlineStr"/>
       <c r="AR113" t="inlineStr"/>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="inlineStr"/>
       <c r="AU113" t="inlineStr"/>
       <c r="AV113" t="inlineStr"/>
@@ -16558,7 +15946,7 @@
       <c r="CA113" t="inlineStr"/>
       <c r="CB113" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16569,30 +15957,14 @@
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Kandarpada</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>कांदरपाडा</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
@@ -16605,20 +15977,12 @@
       <c r="T114" t="inlineStr"/>
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>Kandarpada</t>
-        </is>
-      </c>
+      <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
       <c r="AA114" t="inlineStr"/>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr"/>
       <c r="AE114" t="inlineStr"/>
@@ -16635,11 +15999,7 @@
       <c r="AP114" t="inlineStr"/>
       <c r="AQ114" t="inlineStr"/>
       <c r="AR114" t="inlineStr"/>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="inlineStr"/>
       <c r="AU114" t="inlineStr"/>
       <c r="AV114" t="inlineStr"/>
@@ -16676,7 +16036,7 @@
       <c r="CA114" t="inlineStr"/>
       <c r="CB114" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16687,30 +16047,14 @@
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Anand Nagar</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>आनंद नगर</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
@@ -16728,11 +16072,7 @@
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
       <c r="AA115" t="inlineStr"/>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr"/>
       <c r="AD115" t="inlineStr"/>
       <c r="AE115" t="inlineStr"/>
@@ -16749,11 +16089,7 @@
       <c r="AP115" t="inlineStr"/>
       <c r="AQ115" t="inlineStr"/>
       <c r="AR115" t="inlineStr"/>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="inlineStr"/>
       <c r="AU115" t="inlineStr"/>
       <c r="AV115" t="inlineStr"/>
@@ -16790,7 +16126,7 @@
       <c r="CA115" t="inlineStr"/>
       <c r="CB115" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16801,59 +16137,23 @@
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Diamond Garden</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>डायमंड गार्डन</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>डायमंड गार्डन</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Mumbai Metro Line 2</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Diamond Garden</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
@@ -16862,11 +16162,7 @@
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
       <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr"/>
       <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="inlineStr"/>
@@ -16874,37 +16170,17 @@
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
       <c r="AI116" t="inlineStr"/>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>Deshbhakt N. G. Acharya Udyan Diamond Garden</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Deshbhakt N. G. Acharya Udyan Diamond Garden</t>
-        </is>
-      </c>
+      <c r="AJ116" t="inlineStr"/>
+      <c r="AK116" t="inlineStr"/>
       <c r="AL116" t="inlineStr"/>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>देशभक्त ना. ग. आचार्य उद्यान डायमंड गार्डन</t>
-        </is>
-      </c>
+      <c r="AM116" t="inlineStr"/>
       <c r="AN116" t="inlineStr"/>
       <c r="AO116" t="inlineStr"/>
       <c r="AP116" t="inlineStr"/>
       <c r="AQ116" t="inlineStr"/>
       <c r="AR116" t="inlineStr"/>
-      <c r="AS116" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AT116" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="inlineStr"/>
       <c r="AU116" t="inlineStr"/>
       <c r="AV116" t="inlineStr"/>
       <c r="AW116" t="inlineStr"/>
@@ -16940,7 +16216,7 @@
       <c r="CA116" t="inlineStr"/>
       <c r="CB116" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -16951,34 +16227,14 @@
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Shimpoli</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>शिम्पोली</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>शिंपोली</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
@@ -16991,20 +16247,12 @@
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr"/>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>Shimpawali</t>
-        </is>
-      </c>
+      <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
       <c r="AA117" t="inlineStr"/>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr"/>
       <c r="AE117" t="inlineStr"/>
@@ -17021,11 +16269,7 @@
       <c r="AP117" t="inlineStr"/>
       <c r="AQ117" t="inlineStr"/>
       <c r="AR117" t="inlineStr"/>
-      <c r="AS117" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="inlineStr"/>
       <c r="AU117" t="inlineStr"/>
       <c r="AV117" t="inlineStr"/>
@@ -17062,7 +16306,7 @@
       <c r="CA117" t="inlineStr"/>
       <c r="CB117" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17073,37 +16317,17 @@
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Eksar</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>एकसर</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Q116266993</t>
-        </is>
-      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
@@ -17118,11 +16342,7 @@
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
       <c r="AA118" t="inlineStr"/>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr"/>
       <c r="AD118" t="inlineStr"/>
       <c r="AE118" t="inlineStr"/>
@@ -17139,11 +16359,7 @@
       <c r="AP118" t="inlineStr"/>
       <c r="AQ118" t="inlineStr"/>
       <c r="AR118" t="inlineStr"/>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="inlineStr"/>
       <c r="AU118" t="inlineStr"/>
       <c r="AV118" t="inlineStr"/>
@@ -17180,7 +16396,7 @@
       <c r="CA118" t="inlineStr"/>
       <c r="CB118" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17191,46 +16407,18 @@
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Andheri L1</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>अंधेरी</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>अंधेरी</t>
-        </is>
-      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>Q17512034</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>en:Andheri metro station</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
@@ -17244,11 +16432,7 @@
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
       <c r="AA119" t="inlineStr"/>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr"/>
       <c r="AD119" t="inlineStr"/>
       <c r="AE119" t="inlineStr"/>
@@ -17265,11 +16449,7 @@
       <c r="AP119" t="inlineStr"/>
       <c r="AQ119" t="inlineStr"/>
       <c r="AR119" t="inlineStr"/>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="inlineStr"/>
       <c r="AU119" t="inlineStr"/>
       <c r="AV119" t="inlineStr"/>
@@ -17278,16 +16458,8 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="inlineStr"/>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>Andheri Metro Station</t>
-        </is>
-      </c>
+      <c r="BB119" t="inlineStr"/>
+      <c r="BC119" t="inlineStr"/>
       <c r="BD119" t="inlineStr"/>
       <c r="BE119" t="inlineStr"/>
       <c r="BF119" t="inlineStr"/>
@@ -17314,7 +16486,7 @@
       <c r="CA119" t="inlineStr"/>
       <c r="CB119" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17325,33 +16497,17 @@
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Lower Parel</t>
-        </is>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>Q63346703</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
@@ -17365,16 +16521,8 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr"/>
       <c r="AD120" t="inlineStr"/>
       <c r="AE120" t="inlineStr"/>
@@ -17428,7 +16576,7 @@
       <c r="CA120" t="inlineStr"/>
       <c r="CB120" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Suburban/Local Rail</t>
         </is>
       </c>
     </row>
@@ -17439,30 +16587,14 @@
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Airport Colony Station</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Mumbai Metro Line 7A</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
@@ -17480,11 +16612,7 @@
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
       <c r="AA121" t="inlineStr"/>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="inlineStr"/>
       <c r="AD121" t="inlineStr"/>
       <c r="AE121" t="inlineStr"/>
@@ -17501,16 +16629,8 @@
       <c r="AP121" t="inlineStr"/>
       <c r="AQ121" t="inlineStr"/>
       <c r="AR121" t="inlineStr"/>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AT121" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
+      <c r="AS121" t="inlineStr"/>
+      <c r="AT121" t="inlineStr"/>
       <c r="AU121" t="inlineStr"/>
       <c r="AV121" t="inlineStr"/>
       <c r="AW121" t="inlineStr"/>
@@ -17520,21 +16640,9 @@
       <c r="BA121" t="inlineStr"/>
       <c r="BB121" t="inlineStr"/>
       <c r="BC121" t="inlineStr"/>
-      <c r="BD121" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="BE121" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="BF121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
       <c r="BG121" t="inlineStr"/>
       <c r="BH121" t="inlineStr"/>
       <c r="BI121" t="inlineStr"/>
@@ -17558,7 +16666,7 @@
       <c r="CA121" t="inlineStr"/>
       <c r="CB121" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17569,30 +16677,14 @@
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Anik Nagar Bus Depot Station</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Mumbai Metro Line 4</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
@@ -17610,11 +16702,7 @@
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
       <c r="AA122" t="inlineStr"/>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr"/>
@@ -17631,16 +16719,8 @@
       <c r="AP122" t="inlineStr"/>
       <c r="AQ122" t="inlineStr"/>
       <c r="AR122" t="inlineStr"/>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AT122" t="inlineStr">
-        <is>
-          <t>2027-11</t>
-        </is>
-      </c>
+      <c r="AS122" t="inlineStr"/>
+      <c r="AT122" t="inlineStr"/>
       <c r="AU122" t="inlineStr"/>
       <c r="AV122" t="inlineStr"/>
       <c r="AW122" t="inlineStr"/>
@@ -17650,11 +16730,7 @@
       <c r="BA122" t="inlineStr"/>
       <c r="BB122" t="inlineStr"/>
       <c r="BC122" t="inlineStr"/>
-      <c r="BD122" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="BD122" t="inlineStr"/>
       <c r="BE122" t="inlineStr"/>
       <c r="BF122" t="inlineStr"/>
       <c r="BG122" t="inlineStr"/>
@@ -17680,7 +16756,7 @@
       <c r="CA122" t="inlineStr"/>
       <c r="CB122" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17691,30 +16767,14 @@
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Dahisar (East) [Line 7]</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>दहिसर (पूर्व)</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
@@ -17732,11 +16792,7 @@
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
       <c r="AA123" t="inlineStr"/>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr"/>
       <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="inlineStr"/>
@@ -17753,11 +16809,7 @@
       <c r="AP123" t="inlineStr"/>
       <c r="AQ123" t="inlineStr"/>
       <c r="AR123" t="inlineStr"/>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="inlineStr"/>
       <c r="AU123" t="inlineStr"/>
       <c r="AV123" t="inlineStr"/>
@@ -17794,7 +16846,7 @@
       <c r="CA123" t="inlineStr"/>
       <c r="CB123" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17805,30 +16857,14 @@
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Dahisar (East) [Line 2]</t>
-        </is>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>दहिसर (पूर्व)</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
@@ -17846,11 +16882,7 @@
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
       <c r="AA124" t="inlineStr"/>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="inlineStr"/>
       <c r="AE124" t="inlineStr"/>
@@ -17867,11 +16899,7 @@
       <c r="AP124" t="inlineStr"/>
       <c r="AQ124" t="inlineStr"/>
       <c r="AR124" t="inlineStr"/>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="inlineStr"/>
       <c r="AU124" t="inlineStr"/>
       <c r="AV124" t="inlineStr"/>
@@ -17908,7 +16936,7 @@
       <c r="CA124" t="inlineStr"/>
       <c r="CB124" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -17919,51 +16947,23 @@
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Aarey</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>आरे रोड जंक्शन</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>आरे रोड जंक्शन</t>
-        </is>
-      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>Q116271881</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr"/>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
+      <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
       <c r="U125" t="inlineStr"/>
       <c r="V125" t="inlineStr"/>
@@ -17972,11 +16972,7 @@
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
       <c r="AA125" t="inlineStr"/>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr"/>
       <c r="AD125" t="inlineStr"/>
       <c r="AE125" t="inlineStr"/>
@@ -17984,11 +16980,7 @@
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
       <c r="AI125" t="inlineStr"/>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>Oberoi Garden City Aarey</t>
-        </is>
-      </c>
+      <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
       <c r="AM125" t="inlineStr"/>
@@ -17997,11 +16989,7 @@
       <c r="AP125" t="inlineStr"/>
       <c r="AQ125" t="inlineStr"/>
       <c r="AR125" t="inlineStr"/>
-      <c r="AS125" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="inlineStr"/>
       <c r="AU125" t="inlineStr"/>
       <c r="AV125" t="inlineStr"/>
@@ -18038,7 +17026,7 @@
       <c r="CA125" t="inlineStr"/>
       <c r="CB125" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18049,34 +17037,14 @@
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Dindoshi</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>दिंडोशी</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>दिंडोशी</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
@@ -18085,11 +17053,7 @@
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
+      <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr"/>
       <c r="V126" t="inlineStr"/>
@@ -18098,11 +17062,7 @@
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
       <c r="AA126" t="inlineStr"/>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr"/>
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr"/>
@@ -18119,11 +17079,7 @@
       <c r="AP126" t="inlineStr"/>
       <c r="AQ126" t="inlineStr"/>
       <c r="AR126" t="inlineStr"/>
-      <c r="AS126" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="inlineStr"/>
       <c r="AU126" t="inlineStr"/>
       <c r="AV126" t="inlineStr"/>
@@ -18160,7 +17116,7 @@
       <c r="CA126" t="inlineStr"/>
       <c r="CB126" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18171,34 +17127,14 @@
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Kurar</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>कुरार</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>कुरार</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
@@ -18211,20 +17147,12 @@
       <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr"/>
       <c r="V127" t="inlineStr"/>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>Pushpa Park</t>
-        </is>
-      </c>
+      <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
       <c r="AA127" t="inlineStr"/>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr"/>
@@ -18241,11 +17169,7 @@
       <c r="AP127" t="inlineStr"/>
       <c r="AQ127" t="inlineStr"/>
       <c r="AR127" t="inlineStr"/>
-      <c r="AS127" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="inlineStr"/>
       <c r="AU127" t="inlineStr"/>
       <c r="AV127" t="inlineStr"/>
@@ -18282,7 +17206,7 @@
       <c r="CA127" t="inlineStr"/>
       <c r="CB127" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18293,30 +17217,14 @@
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Akurli</t>
-        </is>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>आकुर्ली</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
@@ -18329,20 +17237,12 @@
       <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr"/>
       <c r="V128" t="inlineStr"/>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>Akurli</t>
-        </is>
-      </c>
+      <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
       <c r="AA128" t="inlineStr"/>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr"/>
       <c r="AD128" t="inlineStr"/>
       <c r="AE128" t="inlineStr"/>
@@ -18359,11 +17259,7 @@
       <c r="AP128" t="inlineStr"/>
       <c r="AQ128" t="inlineStr"/>
       <c r="AR128" t="inlineStr"/>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="inlineStr"/>
       <c r="AU128" t="inlineStr"/>
       <c r="AV128" t="inlineStr"/>
@@ -18400,7 +17296,7 @@
       <c r="CA128" t="inlineStr"/>
       <c r="CB128" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18411,39 +17307,19 @@
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Poisar</t>
-        </is>
-      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>पोइसर</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>Poisar</t>
-        </is>
-      </c>
+      <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr"/>
@@ -18456,11 +17332,7 @@
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
       <c r="AA129" t="inlineStr"/>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr"/>
       <c r="AD129" t="inlineStr"/>
       <c r="AE129" t="inlineStr"/>
@@ -18477,11 +17349,7 @@
       <c r="AP129" t="inlineStr"/>
       <c r="AQ129" t="inlineStr"/>
       <c r="AR129" t="inlineStr"/>
-      <c r="AS129" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="inlineStr"/>
       <c r="AU129" t="inlineStr"/>
       <c r="AV129" t="inlineStr"/>
@@ -18518,7 +17386,7 @@
       <c r="CA129" t="inlineStr"/>
       <c r="CB129" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18529,30 +17397,14 @@
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Magathane</t>
-        </is>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>मगाठाणे</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
@@ -18561,11 +17413,7 @@
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr"/>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S130" t="inlineStr"/>
       <c r="T130" t="inlineStr"/>
       <c r="U130" t="inlineStr"/>
       <c r="V130" t="inlineStr"/>
@@ -18574,16 +17422,8 @@
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
       <c r="AA130" t="inlineStr"/>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AB130" t="inlineStr"/>
+      <c r="AC130" t="inlineStr"/>
       <c r="AD130" t="inlineStr"/>
       <c r="AE130" t="inlineStr"/>
       <c r="AF130" t="inlineStr"/>
@@ -18599,11 +17439,7 @@
       <c r="AP130" t="inlineStr"/>
       <c r="AQ130" t="inlineStr"/>
       <c r="AR130" t="inlineStr"/>
-      <c r="AS130" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="inlineStr"/>
       <c r="AU130" t="inlineStr"/>
       <c r="AV130" t="inlineStr"/>
@@ -18640,7 +17476,7 @@
       <c r="CA130" t="inlineStr"/>
       <c r="CB130" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18651,30 +17487,14 @@
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Devipada</t>
-        </is>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>देवीपाडा</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
@@ -18692,11 +17512,7 @@
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
       <c r="AA131" t="inlineStr"/>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr"/>
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="inlineStr"/>
@@ -18713,11 +17529,7 @@
       <c r="AP131" t="inlineStr"/>
       <c r="AQ131" t="inlineStr"/>
       <c r="AR131" t="inlineStr"/>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="inlineStr"/>
       <c r="AU131" t="inlineStr"/>
       <c r="AV131" t="inlineStr"/>
@@ -18754,7 +17566,7 @@
       <c r="CA131" t="inlineStr"/>
       <c r="CB131" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18765,34 +17577,14 @@
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Gundavali</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>गुंदावली</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>गुंदवली</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
@@ -18801,11 +17593,7 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
       <c r="V132" t="inlineStr"/>
@@ -18814,11 +17602,7 @@
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
       <c r="AA132" t="inlineStr"/>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr"/>
@@ -18835,11 +17619,7 @@
       <c r="AP132" t="inlineStr"/>
       <c r="AQ132" t="inlineStr"/>
       <c r="AR132" t="inlineStr"/>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="inlineStr"/>
       <c r="AU132" t="inlineStr"/>
       <c r="AV132" t="inlineStr"/>
@@ -18876,7 +17656,7 @@
       <c r="CA132" t="inlineStr"/>
       <c r="CB132" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -18887,30 +17667,14 @@
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Mogra</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>मोगरा</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
@@ -18928,11 +17692,7 @@
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
       <c r="AA133" t="inlineStr"/>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr"/>
       <c r="AD133" t="inlineStr"/>
       <c r="AE133" t="inlineStr"/>
@@ -18949,11 +17709,7 @@
       <c r="AP133" t="inlineStr"/>
       <c r="AQ133" t="inlineStr"/>
       <c r="AR133" t="inlineStr"/>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="inlineStr"/>
       <c r="AU133" t="inlineStr"/>
       <c r="AV133" t="inlineStr"/>
@@ -18990,7 +17746,7 @@
       <c r="CA133" t="inlineStr"/>
       <c r="CB133" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19001,30 +17757,14 @@
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Jogeshwari (East)</t>
-        </is>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>जोगेश्वरी (पूर्व)</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
@@ -19042,11 +17782,7 @@
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
       <c r="AA134" t="inlineStr"/>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr"/>
       <c r="AD134" t="inlineStr"/>
       <c r="AE134" t="inlineStr"/>
@@ -19063,11 +17799,7 @@
       <c r="AP134" t="inlineStr"/>
       <c r="AQ134" t="inlineStr"/>
       <c r="AR134" t="inlineStr"/>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="inlineStr"/>
       <c r="AU134" t="inlineStr"/>
       <c r="AV134" t="inlineStr"/>
@@ -19104,7 +17836,7 @@
       <c r="CA134" t="inlineStr"/>
       <c r="CB134" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19115,34 +17847,14 @@
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Goregaon (East)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>गोरेगाँव (पूर्व)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>गोरेगाव (पूर्व)</t>
-        </is>
-      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
@@ -19160,11 +17872,7 @@
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
       <c r="AA135" t="inlineStr"/>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr"/>
       <c r="AD135" t="inlineStr"/>
       <c r="AE135" t="inlineStr"/>
@@ -19172,11 +17880,7 @@
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
       <c r="AI135" t="inlineStr"/>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>Zurich Kotak Goregaon (East)</t>
-        </is>
-      </c>
+      <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="inlineStr"/>
       <c r="AL135" t="inlineStr"/>
       <c r="AM135" t="inlineStr"/>
@@ -19185,11 +17889,7 @@
       <c r="AP135" t="inlineStr"/>
       <c r="AQ135" t="inlineStr"/>
       <c r="AR135" t="inlineStr"/>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="inlineStr"/>
       <c r="AU135" t="inlineStr"/>
       <c r="AV135" t="inlineStr"/>
@@ -19226,7 +17926,7 @@
       <c r="CA135" t="inlineStr"/>
       <c r="CB135" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19237,34 +17937,14 @@
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Andheri (West)</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>अंधेरी (पूर्व)</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>अंधेरी (पश्चिम)</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
@@ -19273,11 +17953,7 @@
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
+      <c r="S136" t="inlineStr"/>
       <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr"/>
       <c r="V136" t="inlineStr"/>
@@ -19286,11 +17962,7 @@
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
       <c r="AA136" t="inlineStr"/>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="inlineStr"/>
       <c r="AE136" t="inlineStr"/>
@@ -19307,11 +17979,7 @@
       <c r="AP136" t="inlineStr"/>
       <c r="AQ136" t="inlineStr"/>
       <c r="AR136" t="inlineStr"/>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="inlineStr"/>
       <c r="AU136" t="inlineStr"/>
       <c r="AV136" t="inlineStr"/>
@@ -19348,7 +18016,7 @@
       <c r="CA136" t="inlineStr"/>
       <c r="CB136" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19359,34 +18027,14 @@
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Lower Oshiwara</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>लोअर ओशिवरा</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>लोअर ओशिवरा</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
@@ -19395,11 +18043,7 @@
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr"/>
       <c r="V137" t="inlineStr"/>
@@ -19408,11 +18052,7 @@
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
       <c r="AA137" t="inlineStr"/>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr"/>
@@ -19429,11 +18069,7 @@
       <c r="AP137" t="inlineStr"/>
       <c r="AQ137" t="inlineStr"/>
       <c r="AR137" t="inlineStr"/>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="inlineStr"/>
       <c r="AU137" t="inlineStr"/>
       <c r="AV137" t="inlineStr"/>
@@ -19470,7 +18106,7 @@
       <c r="CA137" t="inlineStr"/>
       <c r="CB137" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19481,39 +18117,15 @@
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Oshiwara</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>ओशिवारा</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>ओशिवारा</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
@@ -19530,11 +18142,7 @@
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
       <c r="AA138" t="inlineStr"/>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB138" t="inlineStr"/>
       <c r="AC138" t="inlineStr"/>
       <c r="AD138" t="inlineStr"/>
       <c r="AE138" t="inlineStr"/>
@@ -19551,11 +18159,7 @@
       <c r="AP138" t="inlineStr"/>
       <c r="AQ138" t="inlineStr"/>
       <c r="AR138" t="inlineStr"/>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="inlineStr"/>
       <c r="AU138" t="inlineStr"/>
       <c r="AV138" t="inlineStr"/>
@@ -19592,7 +18196,7 @@
       <c r="CA138" t="inlineStr"/>
       <c r="CB138" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19603,34 +18207,14 @@
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Goregaon (West)</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>गोरेगाँव (पश्चिम)</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>गोरेगाँव (पश्चिम)</t>
-        </is>
-      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
@@ -19648,11 +18232,7 @@
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
       <c r="AA139" t="inlineStr"/>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr"/>
       <c r="AD139" t="inlineStr"/>
       <c r="AE139" t="inlineStr"/>
@@ -19669,11 +18249,7 @@
       <c r="AP139" t="inlineStr"/>
       <c r="AQ139" t="inlineStr"/>
       <c r="AR139" t="inlineStr"/>
-      <c r="AS139" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="inlineStr"/>
       <c r="AU139" t="inlineStr"/>
       <c r="AV139" t="inlineStr"/>
@@ -19710,7 +18286,7 @@
       <c r="CA139" t="inlineStr"/>
       <c r="CB139" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19721,37 +18297,17 @@
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Lower Malad</t>
-        </is>
-      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>लोअर मालाड</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>Q116188743</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
@@ -19766,11 +18322,7 @@
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
       <c r="AA140" t="inlineStr"/>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="inlineStr"/>
       <c r="AE140" t="inlineStr"/>
@@ -19787,11 +18339,7 @@
       <c r="AP140" t="inlineStr"/>
       <c r="AQ140" t="inlineStr"/>
       <c r="AR140" t="inlineStr"/>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="inlineStr"/>
       <c r="AU140" t="inlineStr"/>
       <c r="AV140" t="inlineStr"/>
@@ -19828,7 +18376,7 @@
       <c r="CA140" t="inlineStr"/>
       <c r="CB140" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19839,37 +18387,17 @@
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Malad (West)</t>
-        </is>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>मालाड (पश्चिम)</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>Q116188743</t>
-        </is>
-      </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
@@ -19884,11 +18412,7 @@
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
       <c r="AA141" t="inlineStr"/>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="inlineStr"/>
@@ -19905,11 +18429,7 @@
       <c r="AP141" t="inlineStr"/>
       <c r="AQ141" t="inlineStr"/>
       <c r="AR141" t="inlineStr"/>
-      <c r="AS141" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="inlineStr"/>
       <c r="AU141" t="inlineStr"/>
       <c r="AV141" t="inlineStr"/>
@@ -19946,7 +18466,7 @@
       <c r="CA141" t="inlineStr"/>
       <c r="CB141" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -19957,37 +18477,17 @@
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Valnai-Meeth Chowky</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>वळनई-मीठ चौकी</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>Q116188743</t>
-        </is>
-      </c>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
@@ -20002,11 +18502,7 @@
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
       <c r="AA142" t="inlineStr"/>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr"/>
@@ -20023,11 +18519,7 @@
       <c r="AP142" t="inlineStr"/>
       <c r="AQ142" t="inlineStr"/>
       <c r="AR142" t="inlineStr"/>
-      <c r="AS142" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="inlineStr"/>
       <c r="AU142" t="inlineStr"/>
       <c r="AV142" t="inlineStr"/>
@@ -20064,7 +18556,7 @@
       <c r="CA142" t="inlineStr"/>
       <c r="CB142" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20075,34 +18567,14 @@
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Bangur Nagar</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>बांगुर नगर</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>बांगुर नगर</t>
-        </is>
-      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
@@ -20115,24 +18587,12 @@
       <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>Pahadi Goregaon</t>
-        </is>
-      </c>
+      <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>पहाडी गोरेगाव</t>
-        </is>
-      </c>
+      <c r="Z143" t="inlineStr"/>
       <c r="AA143" t="inlineStr"/>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr"/>
       <c r="AD143" t="inlineStr"/>
       <c r="AE143" t="inlineStr"/>
@@ -20149,11 +18609,7 @@
       <c r="AP143" t="inlineStr"/>
       <c r="AQ143" t="inlineStr"/>
       <c r="AR143" t="inlineStr"/>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="inlineStr"/>
       <c r="AU143" t="inlineStr"/>
       <c r="AV143" t="inlineStr"/>
@@ -20190,7 +18646,7 @@
       <c r="CA143" t="inlineStr"/>
       <c r="CB143" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20201,48 +18657,20 @@
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Mandale</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>मंडाले</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>मंडाले</t>
-        </is>
-      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>Mandale</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr"/>
@@ -20254,11 +18682,7 @@
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
       <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="inlineStr"/>
@@ -20275,11 +18699,7 @@
       <c r="AP144" t="inlineStr"/>
       <c r="AQ144" t="inlineStr"/>
       <c r="AR144" t="inlineStr"/>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="inlineStr"/>
       <c r="AU144" t="inlineStr"/>
       <c r="AV144" t="inlineStr"/>
@@ -20316,7 +18736,7 @@
       <c r="CA144" t="inlineStr"/>
       <c r="CB144" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20327,44 +18747,20 @@
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Deonar</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>देवनार</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Deonar</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
       <c r="R145" t="inlineStr"/>
       <c r="S145" t="inlineStr"/>
@@ -20376,21 +18772,13 @@
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
       <c r="AA145" t="inlineStr"/>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr"/>
       <c r="AE145" t="inlineStr"/>
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>BSNL</t>
-        </is>
-      </c>
+      <c r="AH145" t="inlineStr"/>
       <c r="AI145" t="inlineStr"/>
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="inlineStr"/>
@@ -20401,11 +18789,7 @@
       <c r="AP145" t="inlineStr"/>
       <c r="AQ145" t="inlineStr"/>
       <c r="AR145" t="inlineStr"/>
-      <c r="AS145" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="inlineStr"/>
       <c r="AU145" t="inlineStr"/>
       <c r="AV145" t="inlineStr"/>
@@ -20442,7 +18826,7 @@
       <c r="CA145" t="inlineStr"/>
       <c r="CB145" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20453,48 +18837,20 @@
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Mankhurd</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>मानखुर्द</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>मानखुर्द</t>
-        </is>
-      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Mankhurd</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>2026-04-04</t>
-        </is>
-      </c>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
       <c r="R146" t="inlineStr"/>
       <c r="S146" t="inlineStr"/>
@@ -20506,11 +18862,7 @@
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
       <c r="AA146" t="inlineStr"/>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr"/>
       <c r="AD146" t="inlineStr"/>
       <c r="AE146" t="inlineStr"/>
@@ -20527,11 +18879,7 @@
       <c r="AP146" t="inlineStr"/>
       <c r="AQ146" t="inlineStr"/>
       <c r="AR146" t="inlineStr"/>
-      <c r="AS146" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="inlineStr"/>
       <c r="AU146" t="inlineStr"/>
       <c r="AV146" t="inlineStr"/>
@@ -20568,7 +18916,7 @@
       <c r="CA146" t="inlineStr"/>
       <c r="CB146" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Suburban/Local Rail</t>
         </is>
       </c>
     </row>
@@ -20579,33 +18927,17 @@
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Antop Hill</t>
-        </is>
-      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>Q63346708</t>
-        </is>
-      </c>
+      <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
@@ -20619,16 +18951,8 @@
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>monorail</t>
-        </is>
-      </c>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="inlineStr"/>
       <c r="AE147" t="inlineStr"/>
@@ -20643,11 +18967,7 @@
       <c r="AN147" t="inlineStr"/>
       <c r="AO147" t="inlineStr"/>
       <c r="AP147" t="inlineStr"/>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>GTB Nagar</t>
-        </is>
-      </c>
+      <c r="AQ147" t="inlineStr"/>
       <c r="AR147" t="inlineStr"/>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="inlineStr"/>
@@ -20686,7 +19006,7 @@
       <c r="CA147" t="inlineStr"/>
       <c r="CB147" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20697,44 +19017,20 @@
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Dahisar (East) [Line 9]</t>
-        </is>
-      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>दहिसर (पूर्व) [लाईन ९]</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>Dahisar (East) [Line 9]</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
       <c r="R148" t="inlineStr"/>
       <c r="S148" t="inlineStr"/>
@@ -20746,11 +19042,7 @@
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
       <c r="AA148" t="inlineStr"/>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr"/>
       <c r="AD148" t="inlineStr"/>
       <c r="AE148" t="inlineStr"/>
@@ -20767,11 +19059,7 @@
       <c r="AP148" t="inlineStr"/>
       <c r="AQ148" t="inlineStr"/>
       <c r="AR148" t="inlineStr"/>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="inlineStr"/>
       <c r="AU148" t="inlineStr"/>
       <c r="AV148" t="inlineStr"/>
@@ -20808,7 +19096,7 @@
       <c r="CA148" t="inlineStr"/>
       <c r="CB148" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20819,44 +19107,20 @@
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Pandurang Wadi</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>पांडुरंग वाडी</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>Pandurang Wadi</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
       <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
@@ -20868,11 +19132,7 @@
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
       <c r="AA149" t="inlineStr"/>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="inlineStr"/>
       <c r="AE149" t="inlineStr"/>
@@ -20889,11 +19149,7 @@
       <c r="AP149" t="inlineStr"/>
       <c r="AQ149" t="inlineStr"/>
       <c r="AR149" t="inlineStr"/>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="inlineStr"/>
       <c r="AU149" t="inlineStr"/>
       <c r="AV149" t="inlineStr"/>
@@ -20930,7 +19186,7 @@
       <c r="CA149" t="inlineStr"/>
       <c r="CB149" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -20941,59 +19197,23 @@
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>D. N. Nagar</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>डी. एन. नगर</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>डी. एन. नगर</t>
-        </is>
-      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>DNG</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Q17512769</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>D. N. Nagar</t>
-        </is>
-      </c>
+      <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
       <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S150" t="inlineStr"/>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
       <c r="V150" t="inlineStr"/>
@@ -21002,11 +19222,7 @@
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
       <c r="AA150" t="inlineStr"/>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="inlineStr"/>
       <c r="AE150" t="inlineStr"/>
@@ -21014,36 +19230,16 @@
       <c r="AG150" t="inlineStr"/>
       <c r="AH150" t="inlineStr"/>
       <c r="AI150" t="inlineStr"/>
-      <c r="AJ150" t="inlineStr">
-        <is>
-          <t>Vivo D N Nagar</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>Vivo D N Nagar</t>
-        </is>
-      </c>
-      <c r="AL150" t="inlineStr">
-        <is>
-          <t>विवो डी एन नगर</t>
-        </is>
-      </c>
-      <c r="AM150" t="inlineStr">
-        <is>
-          <t>विवो डी एन नगर</t>
-        </is>
-      </c>
+      <c r="AJ150" t="inlineStr"/>
+      <c r="AK150" t="inlineStr"/>
+      <c r="AL150" t="inlineStr"/>
+      <c r="AM150" t="inlineStr"/>
       <c r="AN150" t="inlineStr"/>
       <c r="AO150" t="inlineStr"/>
       <c r="AP150" t="inlineStr"/>
       <c r="AQ150" t="inlineStr"/>
       <c r="AR150" t="inlineStr"/>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="inlineStr"/>
       <c r="AU150" t="inlineStr"/>
       <c r="AV150" t="inlineStr"/>
@@ -21052,11 +19248,7 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="inlineStr"/>
-      <c r="BB150" t="inlineStr">
-        <is>
-          <t>train_station</t>
-        </is>
-      </c>
+      <c r="BB150" t="inlineStr"/>
       <c r="BC150" t="inlineStr"/>
       <c r="BD150" t="inlineStr"/>
       <c r="BE150" t="inlineStr"/>
@@ -21074,16 +19266,8 @@
       <c r="BQ150" t="inlineStr"/>
       <c r="BR150" t="inlineStr"/>
       <c r="BS150" t="inlineStr"/>
-      <c r="BT150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BU150" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="BT150" t="inlineStr"/>
+      <c r="BU150" t="inlineStr"/>
       <c r="BV150" t="inlineStr"/>
       <c r="BW150" t="inlineStr"/>
       <c r="BX150" t="inlineStr"/>
@@ -21092,7 +19276,7 @@
       <c r="CA150" t="inlineStr"/>
       <c r="CB150" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -21103,34 +19287,14 @@
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Azad Nagar</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>आज़ाद नगर</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>आझाद नगर</t>
-        </is>
-      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
@@ -21148,11 +19312,7 @@
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
       <c r="AA151" t="inlineStr"/>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="inlineStr"/>
       <c r="AE151" t="inlineStr"/>
@@ -21169,11 +19329,7 @@
       <c r="AP151" t="inlineStr"/>
       <c r="AQ151" t="inlineStr"/>
       <c r="AR151" t="inlineStr"/>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="inlineStr"/>
       <c r="AU151" t="inlineStr"/>
       <c r="AV151" t="inlineStr"/>
@@ -21182,11 +19338,7 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="inlineStr"/>
-      <c r="BB151" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="BB151" t="inlineStr"/>
       <c r="BC151" t="inlineStr"/>
       <c r="BD151" t="inlineStr"/>
       <c r="BE151" t="inlineStr"/>
@@ -21204,11 +19356,7 @@
       <c r="BQ151" t="inlineStr"/>
       <c r="BR151" t="inlineStr"/>
       <c r="BS151" t="inlineStr"/>
-      <c r="BT151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BT151" t="inlineStr"/>
       <c r="BU151" t="inlineStr"/>
       <c r="BV151" t="inlineStr"/>
       <c r="BW151" t="inlineStr"/>
@@ -21218,7 +19366,7 @@
       <c r="CA151" t="inlineStr"/>
       <c r="CB151" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -21229,30 +19377,14 @@
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Western Express Highway</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>पश्चिम द्रुतगती महामार्ग</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
@@ -21261,11 +19393,7 @@
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
       <c r="V152" t="inlineStr"/>
@@ -21274,11 +19402,7 @@
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
       <c r="AA152" t="inlineStr"/>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="inlineStr"/>
       <c r="AE152" t="inlineStr"/>
@@ -21293,17 +19417,9 @@
       <c r="AN152" t="inlineStr"/>
       <c r="AO152" t="inlineStr"/>
       <c r="AP152" t="inlineStr"/>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>WEH</t>
-        </is>
-      </c>
+      <c r="AQ152" t="inlineStr"/>
       <c r="AR152" t="inlineStr"/>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="inlineStr"/>
       <c r="AU152" t="inlineStr"/>
       <c r="AV152" t="inlineStr"/>
@@ -21312,11 +19428,7 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="inlineStr"/>
-      <c r="BB152" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="BB152" t="inlineStr"/>
       <c r="BC152" t="inlineStr"/>
       <c r="BD152" t="inlineStr"/>
       <c r="BE152" t="inlineStr"/>
@@ -21334,11 +19446,7 @@
       <c r="BQ152" t="inlineStr"/>
       <c r="BR152" t="inlineStr"/>
       <c r="BS152" t="inlineStr"/>
-      <c r="BT152" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BT152" t="inlineStr"/>
       <c r="BU152" t="inlineStr"/>
       <c r="BV152" t="inlineStr"/>
       <c r="BW152" t="inlineStr"/>
@@ -21348,7 +19456,7 @@
       <c r="CA152" t="inlineStr"/>
       <c r="CB152" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -21359,34 +19467,14 @@
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Chakala - J.B. Nagar</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>चकाला - जे. बी. नगर</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>चकाला - जे. बी. नगर</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
@@ -21404,11 +19492,7 @@
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
       <c r="AA153" t="inlineStr"/>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="inlineStr"/>
       <c r="AE153" t="inlineStr"/>
@@ -21416,11 +19500,7 @@
       <c r="AG153" t="inlineStr"/>
       <c r="AH153" t="inlineStr"/>
       <c r="AI153" t="inlineStr"/>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>IndusInd Bank Chakala (J.B.Nagar)</t>
-        </is>
-      </c>
+      <c r="AJ153" t="inlineStr"/>
       <c r="AK153" t="inlineStr"/>
       <c r="AL153" t="inlineStr"/>
       <c r="AM153" t="inlineStr"/>
@@ -21429,11 +19509,7 @@
       <c r="AP153" t="inlineStr"/>
       <c r="AQ153" t="inlineStr"/>
       <c r="AR153" t="inlineStr"/>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="inlineStr"/>
       <c r="AU153" t="inlineStr"/>
       <c r="AV153" t="inlineStr"/>
@@ -21442,11 +19518,7 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="inlineStr"/>
-      <c r="BB153" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="BB153" t="inlineStr"/>
       <c r="BC153" t="inlineStr"/>
       <c r="BD153" t="inlineStr"/>
       <c r="BE153" t="inlineStr"/>
@@ -21464,11 +19536,7 @@
       <c r="BQ153" t="inlineStr"/>
       <c r="BR153" t="inlineStr"/>
       <c r="BS153" t="inlineStr"/>
-      <c r="BT153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BT153" t="inlineStr"/>
       <c r="BU153" t="inlineStr"/>
       <c r="BV153" t="inlineStr"/>
       <c r="BW153" t="inlineStr"/>
@@ -21478,7 +19546,7 @@
       <c r="CA153" t="inlineStr"/>
       <c r="CB153" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -21489,34 +19557,14 @@
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Saki Naka</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>साकी नाका</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>साकी नाका</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
@@ -21525,11 +19573,7 @@
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
       <c r="V154" t="inlineStr"/>
@@ -21538,11 +19582,7 @@
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
       <c r="AA154" t="inlineStr"/>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="inlineStr"/>
       <c r="AE154" t="inlineStr"/>
@@ -21559,11 +19599,7 @@
       <c r="AP154" t="inlineStr"/>
       <c r="AQ154" t="inlineStr"/>
       <c r="AR154" t="inlineStr"/>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="inlineStr"/>
       <c r="AU154" t="inlineStr"/>
       <c r="AV154" t="inlineStr"/>
@@ -21572,11 +19608,7 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="inlineStr"/>
-      <c r="BB154" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="BB154" t="inlineStr"/>
       <c r="BC154" t="inlineStr"/>
       <c r="BD154" t="inlineStr"/>
       <c r="BE154" t="inlineStr"/>
@@ -21594,11 +19626,7 @@
       <c r="BQ154" t="inlineStr"/>
       <c r="BR154" t="inlineStr"/>
       <c r="BS154" t="inlineStr"/>
-      <c r="BT154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BT154" t="inlineStr"/>
       <c r="BU154" t="inlineStr"/>
       <c r="BV154" t="inlineStr"/>
       <c r="BW154" t="inlineStr"/>
@@ -21608,7 +19636,7 @@
       <c r="CA154" t="inlineStr"/>
       <c r="CB154" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -21619,30 +19647,14 @@
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Asalpha</t>
-        </is>
-      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>असल्फा</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
@@ -21660,11 +19672,7 @@
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
       <c r="AA155" t="inlineStr"/>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr"/>
       <c r="AD155" t="inlineStr"/>
       <c r="AE155" t="inlineStr"/>
@@ -21681,11 +19689,7 @@
       <c r="AP155" t="inlineStr"/>
       <c r="AQ155" t="inlineStr"/>
       <c r="AR155" t="inlineStr"/>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="inlineStr"/>
       <c r="AU155" t="inlineStr"/>
       <c r="AV155" t="inlineStr"/>
@@ -21694,11 +19698,7 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="inlineStr"/>
-      <c r="BB155" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="BB155" t="inlineStr"/>
       <c r="BC155" t="inlineStr"/>
       <c r="BD155" t="inlineStr"/>
       <c r="BE155" t="inlineStr"/>
@@ -21716,11 +19716,7 @@
       <c r="BQ155" t="inlineStr"/>
       <c r="BR155" t="inlineStr"/>
       <c r="BS155" t="inlineStr"/>
-      <c r="BT155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BT155" t="inlineStr"/>
       <c r="BU155" t="inlineStr"/>
       <c r="BV155" t="inlineStr"/>
       <c r="BW155" t="inlineStr"/>
@@ -21730,7 +19726,7 @@
       <c r="CA155" t="inlineStr"/>
       <c r="CB155" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
@@ -21741,47 +19737,23 @@
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Kurla</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>3;4</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
+      <c r="S156" t="inlineStr"/>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
       <c r="V156" t="inlineStr"/>
@@ -21838,25 +19810,13 @@
       <c r="BU156" t="inlineStr"/>
       <c r="BV156" t="inlineStr"/>
       <c r="BW156" t="inlineStr"/>
-      <c r="BX156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BY156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="BZ156" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="BX156" t="inlineStr"/>
+      <c r="BY156" t="inlineStr"/>
+      <c r="BZ156" t="inlineStr"/>
       <c r="CA156" t="inlineStr"/>
       <c r="CB156" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Suburban/Local Rail</t>
         </is>
       </c>
     </row>
@@ -21867,26 +19827,14 @@
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Eksar</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>station</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
@@ -21904,11 +19852,7 @@
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr"/>
       <c r="AA157" t="inlineStr"/>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>subway</t>
-        </is>
-      </c>
+      <c r="AB157" t="inlineStr"/>
       <c r="AC157" t="inlineStr"/>
       <c r="AD157" t="inlineStr"/>
       <c r="AE157" t="inlineStr"/>
@@ -21925,11 +19869,7 @@
       <c r="AP157" t="inlineStr"/>
       <c r="AQ157" t="inlineStr"/>
       <c r="AR157" t="inlineStr"/>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="inlineStr"/>
       <c r="AU157" t="inlineStr"/>
       <c r="AV157" t="inlineStr"/>
@@ -21938,11 +19878,7 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="inlineStr"/>
-      <c r="BB157" t="inlineStr">
-        <is>
-          <t>transportation</t>
-        </is>
-      </c>
+      <c r="BB157" t="inlineStr"/>
       <c r="BC157" t="inlineStr"/>
       <c r="BD157" t="inlineStr"/>
       <c r="BE157" t="inlineStr"/>
@@ -21960,11 +19896,7 @@
       <c r="BQ157" t="inlineStr"/>
       <c r="BR157" t="inlineStr"/>
       <c r="BS157" t="inlineStr"/>
-      <c r="BT157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="BT157" t="inlineStr"/>
       <c r="BU157" t="inlineStr"/>
       <c r="BV157" t="inlineStr"/>
       <c r="BW157" t="inlineStr"/>
@@ -21974,7 +19906,7 @@
       <c r="CA157" t="inlineStr"/>
       <c r="CB157" t="inlineStr">
         <is>
-          <t>Unknown/Other System</t>
+          <t>Subway</t>
         </is>
       </c>
     </row>
